--- a/docs/research/provinces/SportsHub-Territories-YT-NWT-NU.xlsx
+++ b/docs/research/provinces/SportsHub-Territories-YT-NWT-NU.xlsx
@@ -11,12 +11,14 @@
     <sheet name="Leagues" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Club-League Map" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Contacts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Club Sizes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$P$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leagues'!$A$1:$L$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Club-League Map'!$A$1:$E$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Contacts'!$A$1:$F$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Club Sizes'!$A$1:$C$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -572,7 +574,6 @@
           <t>recreationculturemanager@cambridgebay.ca</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Daisy Dyer-Eyegetok — women's team coach (reported; overall organizer not published)</t>
@@ -593,7 +594,6 @@
           <t>community program (informal, fields territorial-championship teams)</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>reported</t>
@@ -671,7 +671,6 @@
           <t>multi-sport org (municipal recreation department)</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -709,11 +708,6 @@
           <t>Hay River</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>No standalone club found. Youth basketball delivered through the Town of Hay River recreation department: summer day-camp series including a week-long joint Basketball NWT / NWT Soccer camp for 30+ youth ages 5-13 (Spring and Summer Sports series). A local recreational basketball league is referenced in prior mapping but no current official page found.</t>
@@ -729,7 +723,6 @@
           <t>multi-sport org (municipal recreation department)</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -767,7 +760,6 @@
           <t>Inuvik</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>867-777-3040</t>
@@ -778,7 +770,6 @@
           <t>jason_dayman@bdec.learnnet.nt.ca</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Jason Dayman — youth league contact (per NBA Canada 'find a place to play' directory; BDEC = Beaufort Delta Education Council staff)</t>
@@ -799,7 +790,6 @@
           <t>community program (school/rec-facility based)</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -837,8 +827,6 @@
           <t>Iqaluit</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>nunavutbasketball@outlook.com</t>
@@ -916,7 +904,6 @@
           <t>4061 - 4th Avenue, Whitehorse, YT Y1A 1H1</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>admin@basketballyukon.ca</t>
@@ -989,7 +976,6 @@
           <t>Whitehorse</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>(867) 334-8786</t>
@@ -1025,7 +1011,6 @@
           <t>community nonprofit / volunteer-run girls development program (listed under Basketball Yukon youth programs)</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>primary</t>
@@ -1068,7 +1053,6 @@
           <t>4061 4th Avenue, Whitehorse, YT (listed address; shared Sport Yukon building — unconfirmed on club site)</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>wolfpack.bball@northwestel.net</t>
@@ -1305,8 +1289,6 @@
           <t>Yellowknife</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>GOBallyk@gmail.com</t>
@@ -1317,13 +1299,11 @@
           <t>http://www.goballyk.com</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>Girls-only basketball, kindergarten to grade 8; Spring 2026: U6 (born 2020-21), U8 (born 2018-19, intro 3x3), U10 (born 2016-17), Sundays at Range Lake North school (Apr 12-May 31 2026); also summer camp; focus on skill development, fitness, teamwork</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>community nonprofit girls-only club, partnered with Basketball NWT</t>
@@ -1371,8 +1351,6 @@
           <t>Yellowknife</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>GOBallyk@gmail.com</t>
@@ -1383,7 +1361,6 @@
           <t>http://www.goballyk.com</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>Girls-only grassroots program, kindergarten to grade 8. Spring 2026 sessions: U6 (b. 2020-21), U8 (b. 2018-19), U10 (b. 2016-17, incl. 3-on-3 play), Sundays Apr 12 - May 31 2026 at Range Lake North school.</t>
@@ -1399,7 +1376,6 @@
           <t>community nonprofit (girls grassroots club)</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>verified</t>
@@ -1437,8 +1413,6 @@
           <t>Yellowknife</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>bnwttd1@gmail.com</t>
@@ -1511,7 +1485,6 @@
           <t>Yellowknife</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>(867) 446-3850</t>
@@ -1522,7 +1495,6 @@
           <t>emanramos5@gmail.com</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Emmanuel Ramos — Coach (per NNSL coverage)</t>
@@ -1543,7 +1515,6 @@
           <t>community high-performance program (sponsor-named: Winmar; no standalone web presence found)</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>reported</t>
@@ -1581,10 +1552,6 @@
           <t>Yellowknife</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Emmanuel Ramos — head coach (reported in NNSL coverage)</t>
@@ -1605,7 +1572,6 @@
           <t>community club (boys high-performance program, sponsor-named)</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>reported</t>
@@ -1643,7 +1609,6 @@
           <t>Yellowknife</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>867-445-1771</t>
@@ -1721,8 +1686,6 @@
           <t>Yellowknife</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>info@ykravensbasketball.com</t>
@@ -1958,9 +1921,6 @@
           <t>Yukon (Whitehorse)</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Diedre Davidson (867) 334-8786 diedred@gmail.com; Sarah Crane sarahccrane@gmail.com</t>
@@ -2385,15 +2345,11 @@
           <t>U17 boys won a bronze-division title at a Vancouver tournament (beat Swan City U17 57-56)</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2488,9 +2444,6 @@
           <t>Northwest Territories (Inuvik)</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>Jason Dayman, jason_dayman@bdec.learnnet.nt.ca (from NBA directory; likely stale)</t>
@@ -2538,9 +2491,6 @@
           <t>Northwest Territories (Hay River)</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>Susan Gagnier, gagnier@northwestel.net (from NBA directory; likely stale)</t>
@@ -2551,7 +2501,6 @@
           <t>uncertain</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3894,7 +3843,6 @@
           <t>Daisy Dyer-Eyegetok — women's team coach (reported; overall organizer not published)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3954,7 +3902,6 @@
           <t>Jason Dayman — youth league contact (per NBA Canada 'find a place to play' directory; BDEC = Beaufort Delta Education Council staff)</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3967,7 +3914,6 @@
           <t>Iqaluit</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>nunavutbasketball@outlook.com</t>
@@ -3995,7 +3941,6 @@
           <t>Whitehorse</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>admin@basketballyukon.ca</t>
@@ -4055,7 +4000,6 @@
           <t>Whitehorse</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>wolfpack.bball@northwestel.net</t>
@@ -4147,13 +4091,11 @@
           <t>Yellowknife</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>GOBallyk@gmail.com</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>http://www.goballyk.com</t>
@@ -4171,13 +4113,11 @@
           <t>Yellowknife</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>GOBallyk@gmail.com</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>http://www.goballyk.com</t>
@@ -4195,7 +4135,6 @@
           <t>Yellowknife</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>bnwttd1@gmail.com</t>
@@ -4238,7 +4177,6 @@
           <t>Emmanuel Ramos — Coach (per NNSL coverage)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4251,14 +4189,11 @@
           <t>Yellowknife</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Emmanuel Ramos — head coach (reported in NNSL coverage)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4303,7 +4238,6 @@
           <t>Yellowknife</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>info@ykravensbasketball.com</t>
@@ -4324,4 +4258,191 @@
   <autoFilter ref="A1:F17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Teams counted (directional)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Breakdown (league=teams)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Yellowknife Ravens Basketball Club</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Yellowknife Ravens Basketball Club (bo=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GO Ball</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>GO Ball (girls-only basketball club)=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Yellowknife Eagles Basketball</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Yellowknife Eagles Basketball (girls h=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Cambridge Bay</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Nunavut Basketball Territorial Champio=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Iqaluit</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Nunavut Basketball Territorial Champio=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Baker Lake</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Nunavut Basketball Territorial Champio=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Pangnirtung</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Nunavut Basketball Territorial Champio=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Arctic Bay</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Nunavut Basketball Territorial Champio=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Arviat</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Nunavut Basketball Territorial Champio=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Igloolik</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Nunavut Basketball Territorial Champio=1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/research/provinces/SportsHub-Territories-YT-NWT-NU.xlsx
+++ b/docs/research/provinces/SportsHub-Territories-YT-NWT-NU.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Club Sizes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$P$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$Q$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leagues'!$A$1:$L$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Club-League Map'!$A$1:$E$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Contacts'!$A$1:$F$17</definedName>
@@ -65,11 +65,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -454,6 +455,7 @@
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -537,6 +539,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Teams Counted</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1664,6 +1671,9 @@
           <t>Sister program of the boys' Yellowknife Ravens. Instagram/Facebook: @eaglesball.</t>
         </is>
       </c>
+      <c r="Q17" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1736,9 +1746,12 @@
           <t>Site describes it as a growing male basketball program serving Yellowknife and the territories.</t>
         </is>
       </c>
+      <c r="Q18" t="n">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P18"/>
+  <autoFilter ref="A1:Q18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/research/provinces/SportsHub-Territories-YT-NWT-NU.xlsx
+++ b/docs/research/provinces/SportsHub-Territories-YT-NWT-NU.xlsx
@@ -441,7 +441,7 @@
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -471,77 +471,77 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Teams Counted</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Owner/Principal</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Programs</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Leagues</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Software</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>Teams Counted</t>
         </is>
       </c>
     </row>
@@ -556,62 +556,62 @@
           <t>Territories (YT/NWT/NU)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Nunavut</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Cambridge Bay</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>9 Kingmik Street, Cambridge Bay, NU X0B 0C0</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>(867) 983-4683</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>recreationculturemanager@cambridgebay.ca</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Daisy Dyer-Eyegetok — women's team coach (reported; overall organizer not published)</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Organized U19 boys and girls basketball strong enough to field three teams (one men's, two women's) at the 2026 NUBA U19 Territorial Championships — won both divisions plus women's third place.</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Nunavut Basketball Territorial Championships (U19/18U)</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>community program (informal, fields territorial-championship teams)</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>https://nunatsiaq.com/stories/article/cambridge-bay-earns-double-victories-at-nunavut-basketball-championships/</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Strongest of the Nunavut community programs (multiple teams, double 2026 territorial champions). Other communities fielding U19 territorial teams with no discoverable club entity: Iqaluit, Baker Lake, Pangnirtung, Arctic Bay, Arviat, Igloolik — not listed as separate rows to avoid padding with empty entries. | enriched 2026-07-18</t>
         </is>
@@ -628,67 +628,67 @@
           <t>Territories (YT/NWT/NU)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Northwest Territories</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Hay River</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Hay River Community Centre, Hay River, NT</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>867-874-6522</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>townhall@hayriver.com</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>https://hayriver.com/youth-programs/</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Stephane Millette — Director of Recreation and Community Services</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Municipal recreation department; youth programming (After School Club ages 5-10, Summer Heat, sports leagues) at Hay River Community Centre; recreational basketball league previously mapped for this community; adding multi-sport/basketball equipment via $100K national recreation prize</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Hay River recreational basketball league</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>multi-sport org (municipal recreation department)</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>https://hayriver.com/youth-programs/</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>No standalone basketball club exists in Hay River; rec basketball runs through the town recreation department (programming announced via Facebook). Hay River school teams (NTSSA Cager) are out of scope. No club-level youth basketball found in Fort Smith either — nearest hits were Fort Smith, Arkansas (excluded). | Type: municipal recreation department (not a club) offering youth sports leagues/after-school programming at Hay River Community Centre. General town email townhall@hayriver.com; alternate phone 867-874-3237; Facebook facebook.com/HayRiverRec. Principal verified via multiple sources: https://www.linkedin.com/in/stephane-millette-8543b427b/ , Town council minutes https://hayriver.com/wp-content/uploads/2025/05/0224-Regular-Meeting-of-Council-Minutes-.pdf , and https://hayriver.com/parks-recreation/ . Primary source: https://hayriver.com/youth-programs/ .</t>
         </is>
@@ -705,42 +705,42 @@
           <t>Territories (YT/NWT/NU)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Northwest Territories</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Hay River</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>No standalone club found. Youth basketball delivered through the Town of Hay River recreation department: summer day-camp series including a week-long joint Basketball NWT / NWT Soccer camp for 30+ youth ages 5-13 (Spring and Summer Sports series). A local recreational basketball league is referenced in prior mapping but no current official page found.</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Hay River recreational basketball league (existence not independently confirmed online)</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>multi-sport org (municipal recreation department)</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>https://www.nnsl.com/home/a-different-type-of-day-camp-for-hay-river-youth-7472261</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Included to cover the pre-mapped 'Hay River recreational basketball league'. Only verifiable evidence is rec-department camp programming with Basketball NWT; no club entity, contact, or registration page found. Note: Fort Smith similarly has NO dedicated youth basketball club found (school + rec centre only) — intentionally no entry.</t>
         </is>
@@ -757,57 +757,57 @@
           <t>Territories (YT/NWT/NU)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Northwest Territories</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Inuvik</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>867-777-3040</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>jason_dayman@bdec.learnnet.nt.ca</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Jason Dayman — youth league contact (per NBA Canada 'find a place to play' directory; BDEC = Beaufort Delta Education Council staff)</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Community youth basketball league; Inuvik youth/community teams also travel to the Yukon Lights Out Invitational in Whitehorse</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Inuvik youth basketball league; Yukon Lights Out Invitational (travel); Inuvik youth basketball league (self-operated)</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>community program (school/rec-facility based)</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>https://www.yukon-news.com/sports/lights-out-yukon-invitational-basketball-tournament-bigger-than-ever-in-sixth-year-6998654</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Contact sourced from the now-offline nba.ecrew.ca NT directory (via search index) — may be stale. Town of Inuvik Midnight Sun Complex runs general youth rec programming (Recreation Coordinator 867-777-8640) but no dedicated basketball page found.</t>
         </is>
@@ -824,62 +824,62 @@
           <t>Territories (YT/NWT/NU)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Nunavut</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Iqaluit</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>nunavutbasketball@outlook.com</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>https://www.nunavutbasketball.ca</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Gary Kennedy — President (per Nunatsiaq News championship coverage); Abbas Parks — Qikiqtani representative, board of directors</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Territorial sport organization formed ~2021 and the sole youth basketball operator in Nunavut: grassroots camps/clinics (3-4 days each) in every region annually, Iqaluit youth clinics and 3-on-3 program, coaching education (Coaching 101), Basketball Day in Nunavut, Team Nunavut (first Canada Summer Games appearance 2025)</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Nunavut Basketball Territorial Championships (U19/18U); NUBA Regional Championships (Kitikmeot/Kivalliq + Qikiqtani); Iqaluit 3-on-3 program; Nunavut Basketball Territorial Championships (U19/18U) (operates); NUBA Regional Championships (Kitikmeot/Kivalliq + Qikiqtani) (operates); Iqaluit 3-on-3 program (operates)</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>territorial governing body (nonprofit) / direct program operator</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Online application forms on own website; no commercial registration platform identified</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>https://www.nunavutbasketball.ca/</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>No standalone youth clubs or private academies found anywhere in Nunavut — basketball is organized entirely through NUBA plus school and community teams (Cambridge Bay is the talent hotbed, supplying ~half of Arctic Winter Games rosters). Iqaluit Basketball League on RecLeague.net and Iqaluit Recreational Basketball (Facebook) are adult rec — excluded. Excluded adult-only leagues elsewhere in the territories: Yellowknife Basketball Association, Yellowknife Philippine Basketball League, Yellowknife Women's Basketball, Yukon Men's Basketball League, Whitehorse Women's Basketball League, Filipino Canadian Basketball League of Yukon (runs on TeamLinkt — platform intel) and CFSAY (LeagueLineup).</t>
         </is>
@@ -896,67 +896,67 @@
           <t>Territories (YT/NWT/NU)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Yukon</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Whitehorse</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>4061 - 4th Avenue, Whitehorse, YT Y1A 1H1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>admin@basketballyukon.ca</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>https://basketballyukon.ca</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Corinna Warren — President</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Territorial sport organization (PSO): youth programs (lists Wolf Pack and Lynx as delivery partners), adult leagues, high-performance/Team Yukon, coach and officials development, athlete funding</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Yukon Lights Out Invitational (co-presenter with Aasman Brand Communications); Jr. NBA Yukon (delivered via Wolf Pack)</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>territorial governing body (community nonprofit)</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>WordPress site; no registration platform identified</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>https://basketballyukon.ca/</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Included because in the territories the PSO is a direct program/league operator. Board names could not be verified on official site (search-result board list appeared to be misattributed from a community league — omitted). Yukon Lights Out is a tournament, not a season league. | Type: territorial governing body (PSO) that also directly runs the youth club programming in Whitehorse (no separate community clubs found besides Wolf Pack). Board verified on https://basketballyukon.ca/board-members/ : Corinna Warren (President), Randi Lapushinsky (Treasurer), members-at-large Diedre Davidson, Claire Abbott, Marshal Johnson, Luke Mahilum, Joselito Tobias, Vincent Bonnay. No executive director or org phone listed. Youth-programs contact per basketballyukon.ca/youth-programs/ search snippet: Diedre Davidson (867) 334-8786, diedred@gmail.com (personal cell — kept out of phone field). Sources: https://basketballyukon.ca/ , https://basketballyukon.ca/board-members/ , https://basketballyukon.ca/youth-programs/ .</t>
         </is>
@@ -973,62 +973,62 @@
           <t>Territories (YT/NWT/NU)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Yukon</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Whitehorse</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>(867) 334-8786</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>diedred@gmail.com</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>https://www.facebook.com/lynxbballyukon/</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Diedre Davidson — Program Coordinator; Sarah Crane — co-organizer (sarahccrane@gmail.com)</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Girls-only skills training and development for girls/young women in Yukon; inclusive, low-pressure programming; has fielded Whitehorse Lynx teams at cross-border games (e.g., Skagway, AK)</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Lynx Basketball (girls development program — internal sessions)</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>community nonprofit / volunteer-run girls development program (listed under Basketball Yukon youth programs)</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>https://basketballyukon.ca/youth-programs/</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Contact info published on Basketball Yukon's official youth-programs page. Instagram: @lynxbasketballclub. | Also listed as: Lynx Basketball Club</t>
         </is>
@@ -1045,67 +1045,67 @@
           <t>Territories (YT/NWT/NU)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Yukon</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Whitehorse</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>4061 4th Avenue, Whitehorse, YT (listed address; shared Sport Yukon building — unconfirmed on club site)</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>wolfpack.bball@northwestel.net</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>https://www.wolfpack-basketball.com</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Tim Brady — coach/program lead (quoted as club leader; no formal president/founder title published; club started summer 2015)</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Ages 5-18. Seasonal player development programs, skill camps/clinics, high-performance competitive teams (13U boys, 14U HP boys, 16U boys HP, 15U/16U girls — summer programs CA$250), coach training. Official Jr. NBA delivery in Whitehorse, hosted programs in Pelly Crossing and Dawson City. Canada Basketball verified.</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Jr. NBA Yukon (operates, in partnership with Canada Basketball); Jr. NBA Yukon; Yukon Lights Out Invitational (youth divisions); Out-of-territory tournaments (BC/Alberta/Alaska)</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>community nonprofit club</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Squarespace website with own sign-up forms; no dedicated sports-management platform found</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>https://www.wolfpack-basketball.com/about</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>The only club program in Yukon serving boys; explicitly serves rural Yukon communities. Member/partner of Basketball Yukon. | Also listed as: Wolf Pack Basketball</t>
         </is>
@@ -1122,72 +1122,72 @@
           <t>Territories (YT/NWT/NU)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Northwest Territories</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Yellowknife</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Box 11089, 4908 49 Street, Yellowknife, NT X1A 3X7</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>(867) 445-6421</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>bnwttd1@gmail.com</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>https://bnwt.ca</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Tanya Kearney — Executive Director (appointed Oct 16, 2025); Damien Healy — President</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Operates YK Youth Basketball League (YYBL, U13/U15 divisions, fall-winter), Jr. NBA Yellowknife youth league (formerly Steve Nash Youth Basketball — contact Cole Marshall), U14 Futures Jr. High Performance Program (grade 6-8 boys), territorial HP teams (Team NT), and outreach camps in communities incl. Hay River, Norman Wells and Whatì.</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>YK Youth Basketball League (YYBL) (operates); Jr. NBA Yellowknife youth league (operates; formerly Steve Nash Youth Basketball); U14 Futures Jr. High Performance Program (NWT) (operates)</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>territorial governing body (TSO) — direct league/program operator</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>GOALLINE / Stack Sports (site 'Powered by GOALLINE'; registrations via bnwt.goalline.ca forms)</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>https://bnwt.ca/</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>bnwt.ca returned intermittent HTTP 500s during research; address/phone/ED/president taken from search-indexed copies of its own pages — re-verify before outreach. Key GTM lead: legacy GOALLINE platform (Stack Sports sunset risk) across all BNWT-run youth leagues.</t>
         </is>
@@ -1204,72 +1204,72 @@
           <t>Territories (YT/NWT/NU)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Northwest Territories</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Yellowknife</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Box 11089, 4908 49 Street, Yellowknife, NT X1A 3X7</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>(867) 445-6421</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>bnwttd1@gmail.com</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>https://bnwt.ca</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Cole Marshall — Technical Director (confirmed via Sport North Federation announcement); Executive Director role posted Sept 2025 (SIRC job description)</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Territorial sport organization AND direct youth operator: YK Youth Basketball League (YYBL), Jr. NBA Yellowknife (formerly Steve Nash Youth Basketball, elementary ages), U14 Futures Jr. High Performance Program (boys grades 6-9, 4th year, Instagram @futuresbasketballnwt), community programming in Norman Wells and Whatì, Team NT (Canada Games)</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>YK Youth Basketball League (YYBL); Jr. NBA Yellowknife youth league (formerly Steve Nash Youth Basketball); U14 Futures Jr. High Performance Program (NWT)</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>territorial governing body (registered not-for-profit society) / direct league operator</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>GOALLINE (Stack Sports) — bnwt.goalline.ca for league/program registration; bnwt.ca site also GOALLINE-powered</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>https://bnwt.ca/</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>bnwt.ca GOALLINE pages intermittently return HTTP 500 (site flaky/under construction) — details cross-confirmed via CFMWS Yellowknife directory, Facebook posts and search caches. No club-level youth basketball found in Fort Smith (school/NTSSA Cager teams only, which are out of scope).</t>
         </is>
@@ -1286,52 +1286,52 @@
           <t>Territories (YT/NWT/NU)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Northwest Territories</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Yellowknife</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>GOBallyk@gmail.com</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>http://www.goballyk.com</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Girls-only basketball, kindergarten to grade 8; Spring 2026: U6 (born 2020-21), U8 (born 2018-19, intro 3x3), U10 (born 2016-17), Sundays at Range Lake North school (Apr 12-May 31 2026); also summer camp; focus on skill development, fitness, teamwork</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>community nonprofit girls-only club, partnered with Basketball NWT</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Registers participants through Basketball NWT (BNWT registration required for new participants — GOALLINE platform)</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>http://www.goballyk.com/programs</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Founder/leadership not published on site or found in news. Instagram: @goballyk. | Type: community girls-only youth program (Girls Only Basketball, K-grade 8), partnered with/registered under Basketball NWT; sponsored by McLennan Ross LLP. Programs run at Range Lake North school (Spring 2026). No street address, phone, or named principal published on site, Facebook, or news (checked goballyk.com Contact/Programs/Register pages, Cabin Radio, NNSL). Sources: http://www.goballyk.com/contact-us (email GOBallyk@gmail.com), http://www.goballyk.com/programs , http://www.goballyk.com/register . PLATFORM INTEL: registration via RAMP Registrations (goball.rampregistrations.com).</t>
         </is>
@@ -1348,52 +1348,52 @@
           <t>Territories (YT/NWT/NU)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Northwest Territories</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Yellowknife</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>GOBallyk@gmail.com</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>http://www.goballyk.com</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Girls-only grassroots program, kindergarten to grade 8. Spring 2026 sessions: U6 (b. 2020-21), U8 (b. 2018-19), U10 (b. 2016-17, incl. 3-on-3 play), Sundays Apr 12 - May 31 2026 at Range Lake North school.</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>GO Ball (girls-only basketball club — internal sessions/mini 3-on-3)</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>community nonprofit (girls grassroots club)</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>http://www.goballyk.com/</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Partnered with Basketball NWT; sponsored by McLennan Ross LLP. Organizer names not published. Registration platform not yet posted for 2026 ('Stay tuned for registration dates/details').</t>
         </is>
@@ -1410,62 +1410,62 @@
           <t>Territories (YT/NWT/NU)</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Northwest Territories</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Yellowknife</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>bnwttd1@gmail.com</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>https://www.instagram.com/futuresbasketballnwt/</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Cole Marshall — Head Coach (also Basketball NWT technical staff contact)</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Grade 6-8 boys junior high-performance pool, 4th year of operation; created to prepare athletes for the high-school HP team and Team NT at national/multi-sport events.</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>U14 Futures Jr. High Performance Program (NWT) (is the program itself; feeds Team NT)</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>governing-body high-performance program (Basketball NWT-operated)</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>GOALLINE / Stack Sports (registrations run through parent org Basketball NWT's bnwt.goalline.ca)</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>https://cfmws.ca/yellowknife/basketball</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Program of Basketball NWT, not an independent club — listed separately because it recruits and registers as its own entity (has own Instagram brand).</t>
         </is>
@@ -1482,57 +1482,57 @@
           <t>Territories (YT/NWT/NU)</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Northwest Territories</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Yellowknife</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>(867) 446-3850</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>emanramos5@gmail.com</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Emmanuel Ramos — Coach (per NNSL coverage)</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Boys high-performance program, U17 age group (roster reported at Swoosh Volvo of Edmonton Challenge, won U17 boys bronze division)</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Yellowknife Basketball Association (YKBA senior club league — youth HP team plays up); Out-of-territory tournaments (Swoosh Volvo of Edmonton Challenge)</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>community high-performance program (sponsor-named: Winmar; no standalone web presence found)</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>https://www.nnsl.com/sports/a-winning-weekend-on-the-basketball-court-for-yellowknife-eagles-and-winmar-spartans-7273864</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Known only from NNSL/Yellowknifer sports coverage; article now behind redirect/404 but indexed content confirms coach and tournament results. Likely operates informally alongside BNWT HP structures. YKBA itself is an adult club league (excluded as an entity) that the Spartans compete in. | Type: rep/high-performance boys club (U17/U18, Grades 10-12) under Basketball NWT; plays regular season in Yellowknife Basketball Association (YKBA); 'Winmar' is a sponsor name. No club website of its own — listed on Basketball NWT's directory (bnwt.ca, site returning HTTP 500 during research; contact phone/email taken from indexed bnwt.ca club-listing snippets naming Eman Ramos for Spartans tryouts/registration, corroborated twice). Principal verified by news: head coach Emmanuel Ramos, Yellowknifer/NNSL article https://yellowknifer.com/sports/a-winning-weekend-on-the-basketball-court-for-yellowknife-eagles-and-winmar-spartans . Other sources: http://bnwt.ca/page.php?page_id=124835 (BNWT club pages), http://bnwt.goalline.ca/news.php . PLATFORM INTEL: Basketball NWT/club listings run on GOALLINE (Stack Sports) — bnwt.goalline.ca.</t>
         </is>
@@ -1549,47 +1549,47 @@
           <t>Territories (YT/NWT/NU)</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Northwest Territories</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Yellowknife</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Emmanuel Ramos — head coach (reported in NNSL coverage)</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Boys U17 high-performance team; season play locally plus one travel tournament per season (won U17 boys bronze division at Swoosh Volvo of Edmonton Challenge, beating Swan City U17 57-56).</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>Yellowknife Basketball Association (YKBA) club league</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>community club (boys high-performance program, sponsor-named)</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>https://www.nnsl.com/sports/a-winning-weekend-on-the-basketball-court-for-yellowknife-eagles-and-winmar-spartans-7273864</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Known only through NNSL/Yellowknifer sports coverage; no website or registration page found — likely operates informally alongside the BNWT/Ravens HP stream. 'Winmar' is a sponsor name (Winmar Property Restoration).</t>
         </is>
@@ -1606,73 +1606,73 @@
           <t>Territories (YT/NWT/NU)</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>Northwest Territories</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Yellowknife</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>867-445-1771</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>ykeaglesball@gmail.com</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>https://www.eaglesball.ca</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Aaron Wells — U19 Head Coach (program leadership figure per NNSL; no president/ED published). Other coaches: Richelle Castillo (U13 head), Tina Locke-Setter (U13 asst), Scott Green, Kyla Lesage, Sierra Nesbitt (U19 assts)</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>Girls high-performance club basketball, Grades 6-12: U13 (Gr 7 &amp; under), U15 (Gr 8-9), U17/U19 (Gr 10-12); season Oct-May; descended from early-1990s Yellowknife High Performance Girls Basketball Program</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>Out-of-territory tournaments (e.g., Volvo of Edmonton Challenge); Yellowknife Basketball Association (YKBA) women's league (U19 team, per 2021-22 season reporting)</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>community nonprofit club (girls high-performance; Basketball NWT-affiliated, BNWT logo in footer)</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>RAMP Registrations + Google Forms (both linked from site)</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>https://www.eaglesball.ca/</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Sister program of the boys' Yellowknife Ravens. Instagram/Facebook: @eaglesball.</t>
         </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1686,68 +1686,68 @@
           <t>Territories (YT/NWT/NU)</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Northwest Territories</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Yellowknife</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>info@ykravensbasketball.com</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>https://www.ykravensbasketball.com</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Jose Esteban — Program Director (also Assistant Coach U18); Mark Matheson — Head Coach U18</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>Boys high-performance club basketball: U13 (head coach Kent Alacida), U14 (James Jones), U16 (Narlie Dapilos), U18 (Mark Matheson); volunteer coach recruitment ongoing</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>Out-of-territory tournaments; Yellowknife Basketball Association (YKBA) club league (reported — Ravens entry in YKBA playoffs)</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>community nonprofit club (boys high-performance; sister program to Eagles, Basketball NWT-affiliated)</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>RAMP Registrations (RavensBasketballClub.rampregistrations.com)</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>https://www.ykravensbasketball.com/</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Site describes it as a growing male basketball program serving Yellowknife and the territories.</t>
         </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
